--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130836029</v>
       </c>
       <c r="B2" t="n">
-        <v>97093</v>
+        <v>97102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131007343</v>
       </c>
       <c r="B3" t="n">
-        <v>99014</v>
+        <v>99015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131007342</v>
       </c>
       <c r="B4" t="n">
-        <v>97879</v>
+        <v>97880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131007343</v>
       </c>
       <c r="B3" t="n">
-        <v>99015</v>
+        <v>99018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131007342</v>
       </c>
       <c r="B4" t="n">
-        <v>97880</v>
+        <v>97883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131007343</v>
       </c>
       <c r="B3" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131007342</v>
       </c>
       <c r="B4" t="n">
-        <v>97883</v>
+        <v>97884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131007343</v>
       </c>
       <c r="B3" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131007342</v>
       </c>
       <c r="B4" t="n">
-        <v>97884</v>
+        <v>97886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,219 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134326035</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Siksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>519329</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6672075</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134324692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Siksberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519402</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6672160</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elias Blad, Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130836029</v>
       </c>
       <c r="B2" t="n">
-        <v>97127</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131007343</v>
+        <v>134324692</v>
       </c>
       <c r="B3" t="n">
-        <v>99021</v>
+        <v>57165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kysveden, Dlr</t>
+          <t>Siksberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519522</v>
+        <v>519402</v>
       </c>
       <c r="R3" t="n">
-        <v>6672233</v>
+        <v>6672160</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -837,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Elias Blad, Mårten Wikström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131007342</v>
+        <v>134326023</v>
       </c>
       <c r="B4" t="n">
-        <v>97886</v>
+        <v>57165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +888,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kysveden, Dlr</t>
+          <t>Siksberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519536</v>
+        <v>519460</v>
       </c>
       <c r="R4" t="n">
-        <v>6672276</v>
+        <v>6672328</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -934,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,12 +976,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1074,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134324692</v>
+        <v>134326032</v>
       </c>
       <c r="B6" t="n">
-        <v>57165</v>
+        <v>58131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,16 +1107,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>103023</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1102,12 +1124,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1117,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519402</v>
+        <v>519559</v>
       </c>
       <c r="R6" t="n">
-        <v>6672160</v>
+        <v>6672326</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1172,10 +1197,305 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Blad, Mårten Wikström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130836030</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kysveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519550</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6672328</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131007343</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kysveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>519522</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6672233</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131007342</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kysveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>519536</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6672276</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19410-2023 artfynd.xlsx
+++ b/artfynd/A 19410-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134326035</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130836029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324692</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134326023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134326032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130836030</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131007343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,8 +1536,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131007342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>